--- a/data/trans_orig/P37A$medicoenfermedad-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicoenfermedad-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59446</t>
+          <t>59189</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92029</t>
+          <t>92446</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50454</t>
+          <t>51324</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82119</t>
+          <t>81958</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117759</t>
+          <t>118925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165543</t>
+          <t>165747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>939694</t>
+          <t>939277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>972277</t>
+          <t>972534</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1232994</t>
+          <t>1233155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1264659</t>
+          <t>1263789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2181292</t>
+          <t>2181088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2229076</t>
+          <t>2227910</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19035</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40489</t>
+          <t>38972</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>37284</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40485</t>
+          <t>40819</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70204</t>
+          <t>68564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1652924</t>
+          <t>1654441</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1674378</t>
+          <t>1674961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1549544</t>
+          <t>1550389</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1570743</t>
+          <t>1570766</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3210882</t>
+          <t>3212522</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3240601</t>
+          <t>3240267</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23423</t>
+          <t>23384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531284</t>
+          <t>530810</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546243</t>
+          <t>546282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>469061</t>
+          <t>468988</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>475609</t>
+          <t>475610</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1004397</t>
+          <t>1004436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1021043</t>
+          <t>1020521</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92818</t>
+          <t>93850</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134187</t>
+          <t>134078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76264</t>
+          <t>75676</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114793</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180170</t>
+          <t>179404</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>236111</t>
+          <t>232890</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3142356</t>
+          <t>3142465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3183725</t>
+          <t>3182693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3264404</t>
+          <t>3267006</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3302933</t>
+          <t>3303521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6419630</t>
+          <t>6422851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6475571</t>
+          <t>6476337</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56064</t>
+          <t>55131</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89779</t>
+          <t>89975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69169</t>
+          <t>70207</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106755</t>
+          <t>105758</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133360</t>
+          <t>133832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>184526</t>
+          <t>182590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>884864</t>
+          <t>884668</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>918579</t>
+          <t>919512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1231042</t>
+          <t>1232039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1268628</t>
+          <t>1267590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2127914</t>
+          <t>2129850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2179080</t>
+          <t>2178608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35478</t>
+          <t>35101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63867</t>
+          <t>63626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59785</t>
+          <t>56872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72974</t>
+          <t>73239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113535</t>
+          <t>112095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1900090</t>
+          <t>1900331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1928479</t>
+          <t>1928856</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1698018</t>
+          <t>1700931</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1726591</t>
+          <t>1727518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3608225</t>
+          <t>3609665</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3648786</t>
+          <t>3648521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22790</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28428</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>467465</t>
+          <t>468018</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480052</t>
+          <t>480073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435841</t>
+          <t>436621</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>452220</t>
+          <t>452389</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>911385</t>
+          <t>911198</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>930316</t>
+          <t>930242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103312</t>
+          <t>102856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149427</t>
+          <t>147739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118811</t>
+          <t>119454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165828</t>
+          <t>168227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>239671</t>
+          <t>235396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304536</t>
+          <t>300330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3270355</t>
+          <t>3272043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3316470</t>
+          <t>3316926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3388402</t>
+          <t>3386003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3435419</t>
+          <t>3434776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6669476</t>
+          <t>6673682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6734341</t>
+          <t>6738616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33461</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58975</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39227</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69918</t>
+          <t>67948</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77852</t>
+          <t>78312</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117828</t>
+          <t>118529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>695372</t>
+          <t>695856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>720886</t>
+          <t>719897</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>924742</t>
+          <t>926712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>955433</t>
+          <t>956319</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1631179</t>
+          <t>1630478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1671155</t>
+          <t>1670695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46440</t>
+          <t>45090</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78458</t>
+          <t>78241</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29806</t>
+          <t>32136</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58817</t>
+          <t>58866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84403</t>
+          <t>84494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126017</t>
+          <t>125238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1997927</t>
+          <t>1998144</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2029945</t>
+          <t>2031295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1929483</t>
+          <t>1929434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1958494</t>
+          <t>1956164</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3938668</t>
+          <t>3939447</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3980282</t>
+          <t>3980191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21425</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20605</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35920</t>
+          <t>36622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525461</t>
+          <t>525353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540962</t>
+          <t>541625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>528535</t>
+          <t>528529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>542697</t>
+          <t>542189</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1060107</t>
+          <t>1059405</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1080127</t>
+          <t>1080496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>97536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141536</t>
+          <t>145079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87588</t>
+          <t>87287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130517</t>
+          <t>128358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>194222</t>
+          <t>195524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252994</t>
+          <t>256551</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3236082</t>
+          <t>3232539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3280569</t>
+          <t>3280082</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3401583</t>
+          <t>3403742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3444512</t>
+          <t>3444813</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6656724</t>
+          <t>6653167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6715496</t>
+          <t>6714194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>50474</t>
+          <t>54333</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39326</t>
+          <t>43316</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63638</t>
+          <t>69688</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>99848</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75945</t>
+          <t>85618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101588</t>
+          <t>113990</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>139399</t>
+          <t>154181</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>122732</t>
+          <t>136798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158401</t>
+          <t>173725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>464464</t>
+          <t>524196</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>451300</t>
+          <t>508841</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>475612</t>
+          <t>535213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>666583</t>
+          <t>722190</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653920</t>
+          <t>708048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>679563</t>
+          <t>736420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1131047</t>
+          <t>1246386</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1112045</t>
+          <t>1226842</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1147714</t>
+          <t>1263769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>102590</t>
+          <t>110897</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70646</t>
+          <t>91533</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125886</t>
+          <t>133610</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90236</t>
+          <t>99892</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65743</t>
+          <t>84610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109919</t>
+          <t>117573</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>192826</t>
+          <t>210790</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>149538</t>
+          <t>185155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>223281</t>
+          <t>237773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2187737</t>
+          <t>2119669</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2164441</t>
+          <t>2096956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2219681</t>
+          <t>2139033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2147587</t>
+          <t>2071500</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2127904</t>
+          <t>2053819</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2172080</t>
+          <t>2086782</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4335324</t>
+          <t>4191169</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4304869</t>
+          <t>4164186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4378612</t>
+          <t>4216804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27930</t>
+          <t>31872</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39264</t>
+          <t>43784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30301</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>26545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39613</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>58231</t>
+          <t>67024</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>53658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72124</t>
+          <t>82432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>618693</t>
+          <t>679715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607359</t>
+          <t>667803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627018</t>
+          <t>689422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>630162</t>
+          <t>699725</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>620850</t>
+          <t>688119</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>637491</t>
+          <t>708332</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1248855</t>
+          <t>1379440</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1234962</t>
+          <t>1364032</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1260510</t>
+          <t>1392806</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>180994</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142333</t>
+          <t>172028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209755</t>
+          <t>227771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>209462</t>
+          <t>234892</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167900</t>
+          <t>211098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236352</t>
+          <t>258846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>390456</t>
+          <t>431994</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>333625</t>
+          <t>398492</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>435964</t>
+          <t>468617</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3270895</t>
+          <t>3323581</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3242134</t>
+          <t>3292912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3309556</t>
+          <t>3348655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3444332</t>
+          <t>3493415</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3417442</t>
+          <t>3469461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3485894</t>
+          <t>3517209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6715227</t>
+          <t>6816996</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6669719</t>
+          <t>6780373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6772058</t>
+          <t>6850498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
